--- a/Excel/test.xlsx
+++ b/Excel/test.xlsx
@@ -418,10 +418,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="27.14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
@@ -429,7 +429,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2026年 10月 22日 (四) 26℃ 64% 雨</t>
+          <t>2026年 10月 27日 (二) 26℃ 61% 晴</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -460,157 +460,79 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>升溫30</t>
+          <t>空白升溫30</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>59.64811068856702</v>
+        <v>21.84</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>617.95</v>
+        <v>825</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>升溫40</t>
+          <t>空白升溫40</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>90.45015105740183</v>
+        <v>28.69527483124397</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>513.05</v>
+        <v>777.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>升溫50</t>
+          <t>空白升溫50</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>80.28426862925483</v>
+        <v>31.45050970075633</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>543.5</v>
+        <v>760.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>升溫60</t>
+          <t>空白升溫60</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>109.8912386706949</v>
+        <v>28.72606263262814</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>463.4</v>
+        <v>777.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>升溫70</t>
+          <t>空白升溫70</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>111.0028208744711</v>
+        <v>31.54722569604423</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>460.85</v>
+        <v>759.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>升溫80</t>
+          <t>空白升溫80</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>106.6287018363231</v>
+        <v>34.53839929876611</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>471.05</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>降溫30</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>60.37073170731707</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>降溫40</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>54.95954844778929</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>637.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>降溫50</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>59.58718861209963</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>618.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>降溫60</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>54.03856041131105</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>641.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>降溫70</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>58.94443102198598</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>620.85</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>降溫80</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>62.4921681780709</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>606.5</v>
+        <v>741.55</v>
       </c>
     </row>
   </sheetData>
